--- a/GenC IDP Product Backlog.xlsx
+++ b/GenC IDP Product Backlog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cognizantonline-my.sharepoint.com/personal/2317549_cognizant_com/Documents/Desktop/IDP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2317549\OneDrive - Cognizant\Desktop\IDP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="98" documentId="11_86DDFC7B6A334B6553620E635B45AD79D5C22BEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE4EDD0A-BD20-4EDF-B44B-3866A71A1F32}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02635641-2ECB-4C2B-8958-946877077945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="93">
   <si>
     <t>Product Backlog</t>
   </si>
@@ -463,6 +463,9 @@
   </si>
   <si>
     <t>a+L8</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
   </si>
 </sst>
 </file>
@@ -3153,10 +3156,6 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4151,7 +4150,7 @@
         <v>80</v>
       </c>
       <c r="F9" s="73" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="G9" s="72">
         <v>1</v>
@@ -4174,7 +4173,7 @@
         <v>82</v>
       </c>
       <c r="F10" s="73" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="G10" s="73">
         <v>1</v>
@@ -4472,6 +4471,33 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eac52b12-2228-488c-9d59-8a93d308b64e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735" xsi:nil="true"/>
+    <SharedWithUsers xmlns="951c5514-b77c-4532-82d5-a05f2f7d58e2">
+      <UserInfo>
+        <DisplayName>Ananthan, Aarthi (Cognizant)</DisplayName>
+        <AccountId>30237</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007A9C735C9F3CD54A948D0AD38DF112BF" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d4ed022c10c60e9d9c27ee5a95c8ce3b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eac52b12-2228-488c-9d59-8a93d308b64e" xmlns:ns3="951c5514-b77c-4532-82d5-a05f2f7d58e2" xmlns:ns4="3c35e321-f73a-4dae-ae38-a0459de24735" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c8774e4bcccb30488bd145616ae26a30" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eac52b12-2228-488c-9d59-8a93d308b64e"/>
@@ -4719,34 +4745,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eac52b12-2228-488c-9d59-8a93d308b64e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3c35e321-f73a-4dae-ae38-a0459de24735" xsi:nil="true"/>
-    <SharedWithUsers xmlns="951c5514-b77c-4532-82d5-a05f2f7d58e2">
-      <UserInfo>
-        <DisplayName>Ananthan, Aarthi (Cognizant)</DisplayName>
-        <AccountId>30237</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8575168F-6331-41DA-B879-8152475B9854}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C0C9F9C-98B5-480F-B2D6-CAE7CFAF0133}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="eac52b12-2228-488c-9d59-8a93d308b64e"/>
+    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
+    <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41347413-0C59-4DAA-B1B8-A99F4386EC68}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4764,24 +4783,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C0C9F9C-98B5-480F-B2D6-CAE7CFAF0133}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="eac52b12-2228-488c-9d59-8a93d308b64e"/>
-    <ds:schemaRef ds:uri="3c35e321-f73a-4dae-ae38-a0459de24735"/>
-    <ds:schemaRef ds:uri="951c5514-b77c-4532-82d5-a05f2f7d58e2"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8575168F-6331-41DA-B879-8152475B9854}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>